--- a/autoIt/ImportFiles/AccountImportFromExcel.xlsx
+++ b/autoIt/ImportFiles/AccountImportFromExcel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rakesh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FocusXSanity\FocusAI\autoIt\ImportFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1104,6 +1104,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1114,7 +1115,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1405,77 +1405,77 @@
     <col min="2" max="2" width="9" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="25" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="10" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="10" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="5" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="16" customWidth="1" collapsed="1"/>
     <col min="8" max="10" width="25" customWidth="1" collapsed="1"/>
     <col min="11" max="11" width="10" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7"/>
-      <c r="AQ1" s="7"/>
-      <c r="AR1" s="7"/>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7"/>
-      <c r="AU1" s="7"/>
-      <c r="AV1" s="7"/>
-      <c r="AW1" s="7"/>
-      <c r="AX1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
     </row>
     <row r="2" spans="1:50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:50" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -3956,10 +3956,10 @@
       <c r="C114" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D114" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="10" t="s">
+      <c r="D114" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>20</v>
       </c>
       <c r="F114" t="b">
@@ -3986,11 +3986,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
